--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/one_shot/Contrary(P)Body(N).xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/one_shot/Contrary(P)Body(N).xlsx
@@ -17292,7 +17292,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.623015873015873</v>
+        <v>0.623016</v>
       </c>
     </row>
     <row r="3">
@@ -17351,7 +17351,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.623015873015873</v>
+        <v>0.623016</v>
       </c>
     </row>
     <row r="4">
@@ -17410,7 +17410,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.623015873015873</v>
+        <v>0.623016</v>
       </c>
     </row>
   </sheetData>
